--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519372.1706406561</v>
+        <v>519372</v>
       </c>
       <c r="R3" t="n">
-        <v>6894002.161267285</v>
+        <v>6894002</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +864,9 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,11 +804,6 @@
       </c>
       <c r="E3" t="n">
         <v>219790</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,6 +804,11 @@
       </c>
       <c r="E3" t="n">
         <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2024 artfynd.xlsx
+++ b/artfynd/A 31892-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>82279426</v>
       </c>
       <c r="B3" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
